--- a/i_test/test_D6_Tabella_2_asl_2025/g_output/D6_Table_2_SE.xlsx
+++ b/i_test/test_D6_Tabella_2_asl_2025/g_output/D6_Table_2_SE.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -374,7 +374,7 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1690</t>
+          <t>1678</t>
         </is>
       </c>
     </row>
@@ -388,72 +388,120 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>A10BD</t>
+          <t>1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>1.682 (99,5%)</t>
+          <t>A10BD B10BD B10BX C10BD C10CE 9 (0,5%)</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>A10AE</t>
+          <t>2</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>838 (49,6%)</t>
+          <t>A10AE A10BD B10BD B10BE C10BD 8 (0,5%)</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>A10BH</t>
+          <t>3</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>510 (30,2%)</t>
+          <t>A10AE A10BD A10BJ B10BD C10BD 7 (0,4%)</t>
         </is>
       </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>A10BJ</t>
+          <t>4</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>498 (29,5%)</t>
+          <t>A10AE A10BD B10BD C10BD C10CE 6 (0,4%)</t>
         </is>
       </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>A10BK</t>
+          <t>5</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>477 (28,2%)</t>
+          <t>A10AE A10BD B10BD B10BK C10BD 6 (0,4%)</t>
         </is>
       </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>A10BX</t>
+          <t>6</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>466 (27,6%)</t>
+          <t>A10BD A10BH B10BD C10BD C10CE 5 (0,3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>A10BD A10BH A10BK B10BD C10BD 5 (0,3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>A10BD A10BK B10BD C10BD C10BX 5 (0,3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>A10AE A10BD B10BD B10BJ C10BD 5 (0,3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>A10BD A10BJ B10BD C10BD C10CE 4 (0,2%)</t>
         </is>
       </c>
     </row>

--- a/i_test/test_D6_Tabella_2_asl_2025/g_output/D6_Table_2_SE.xlsx
+++ b/i_test/test_D6_Tabella_2_asl_2025/g_output/D6_Table_2_SE.xlsx
@@ -351,7 +351,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B24"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -374,14 +374,14 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>1678</t>
+          <t>1645</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Combinazioni ATC IV livello (*)</t>
+          <t>Combinazioni di ≥5 ATC IV livello (*)</t>
         </is>
       </c>
     </row>
@@ -393,7 +393,7 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>A10BD B10BD B10BX C10BD C10CE 9 (0,5%)</t>
+          <t>d a B10BD C10BD C10CE 39 (2,4%)</t>
         </is>
       </c>
     </row>
@@ -405,7 +405,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>A10AE A10BD B10BD B10BE C10BD 8 (0,5%)</t>
+          <t>a B10BD C10BD C10CE D15CE 25 (1,5%)</t>
         </is>
       </c>
     </row>
@@ -417,7 +417,7 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>A10AE A10BD A10BJ B10BD C10BD 7 (0,4%)</t>
+          <t>a B10BD C10BD C10CE N10D1 24 (1,5%)</t>
         </is>
       </c>
     </row>
@@ -429,7 +429,7 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>A10AE A10BD B10BD C10BD C10CE 6 (0,4%)</t>
+          <t>d a B10BD C10BD N12BD 23 (1,4%)</t>
         </is>
       </c>
     </row>
@@ -441,7 +441,7 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>A10AE A10BD B10BD B10BK C10BD 6 (0,4%)</t>
+          <t>a B10BD C10BD C10CE N02BJ 23 (1,4%)</t>
         </is>
       </c>
     </row>
@@ -453,7 +453,7 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>A10BD A10BH B10BD C10BD C10CE 5 (0,3%)</t>
+          <t>a B10BD C10BD C10CE N15CE 23 (1,4%)</t>
         </is>
       </c>
     </row>
@@ -465,7 +465,7 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>A10BD A10BH A10BK B10BD C10BD 5 (0,3%)</t>
+          <t>d a B10BD C10BD D18BD 22 (1,3%)</t>
         </is>
       </c>
     </row>
@@ -477,7 +477,7 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>A10BD A10BK B10BD C10BD C10BX 5 (0,3%)</t>
+          <t>a B10BD C10BD C10CE D02BJ 22 (1,3%)</t>
         </is>
       </c>
     </row>
@@ -489,7 +489,7 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>A10AE A10BD B10BD B10BJ C10BD 5 (0,3%)</t>
+          <t>a B10BD C10BD C10CE J01BK 22 (1,3%)</t>
         </is>
       </c>
     </row>
@@ -501,7 +501,134 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>A10BD A10BJ B10BD C10BD C10CE 4 (0,2%)</t>
+          <t>a B10BD C10BD C10CE N03BX 22 (1,3%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>Combinazioni di ≥10 ATC IV livello (*)</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>d a B10BD B10BJ D01BK D02BJ D14CE D17BD D18BD N15CE 2 (0,1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>d a B10BD C10BD C10CE D03BX D18BD J09BD J19BD N09BD 2 (0,1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>d a B10BD C10BD C10CE D03BX D18BD J09BD J19BD N18BD 2 (0,1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>d a B10BD C10BD C10CE D03BX D18BD J09BD N09BD N18BD 2 (0,1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>d a B10BD C10BD C10CE D03BX D18BD J19BD N09BD N18BD 2 (0,1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>d a B10BD C10BD C10CE D03BX J09BD J19BD N09BD N18BD 2 (0,1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>d a B10BD C10BD C10CE D18BD J09BD J19BD N09BD N18BD 2 (0,1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>d a B10BD C10BD D03BX D18BD J09BD J19BD N09BD N18BD 2 (0,1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>d a B10BD C10CE D03BX D18BD J09BD J19BD N09BD N18BD 2 (0,1%)</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B24" t="inlineStr">
+        <is>
+          <t>d a C10BD C10CE D03BX D18BD J09BD J19BD N09BD N18BD 2 (0,1%)</t>
         </is>
       </c>
     </row>
